--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinchen/Documents/GitRepo/websites/csc110/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6F8C35-D2E2-074C-A79A-467200DA521A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8466E-1641-1240-A68E-F6506DBF36B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9140" yWindow="600" windowWidth="36300" windowHeight="25340" xr2:uid="{8E2BECA6-270F-C740-9ED5-1344B6EDB180}"/>
+    <workbookView xWindow="2100" yWindow="600" windowWidth="36300" windowHeight="21000" xr2:uid="{8E2BECA6-270F-C740-9ED5-1344B6EDB180}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2781,7 +2781,7 @@
         <v>46272</v>
       </c>
       <c r="E118" s="5">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="6" t="s">
